--- a/korea-tour-comparison/korea-tour-comparison.xlsx
+++ b/korea-tour-comparison/korea-tour-comparison.xlsx
@@ -10,13 +10,14 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Price" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Days &amp; Flights" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Hotels" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Meals" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Terms" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sightseeing" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sightseeing Opinion" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Hidden Costs" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Days &amp; Flights" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Hotels" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Meals" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Terms" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sightseeing" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sightseeing Opinion" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Notes" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -289,7 +290,149 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Self-paid meals (Meals sheet) × cost per meal (Notes sheet).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Free days × spending per free day (Notes sheet).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Compared with the cheapest of the five 7–8 day spring tours (Rotama excluded: it is a different, 5-day product).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Travel SIM included</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">The Rp 3M discount has a limited quota</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Travel SIM included</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Rp 600k mandatory insurance already counted in the all-in price</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Not stated in brochure: ask Panorama</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F48" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Brochure implies entry is included: confirm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Low-cost airline: meals usually paid</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">"Bagasi sesuai ketentuan airlines" on a low-cost carrier</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -311,7 +454,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -345,7 +488,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -391,7 +534,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -426,7 +569,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="495">
   <si>
     <t xml:space="preserve">Korea Tour Comparison: 6 Packages</t>
   </si>
@@ -515,6 +658,15 @@
     <t xml:space="preserve">Single supplement</t>
   </si>
   <si>
+    <t xml:space="preserve">Estimated hidden costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE TRIP COST (all-in + hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True cost rank (1 = cheapest)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Comfort</t>
   </si>
   <si>
@@ -666,6 +818,285 @@
   </si>
   <si>
     <t xml:space="preserve">Rotama is a 5-day Seoul-only trip in November on a low-cost airline. Compare its price with care. USD tipping converted at the rate on the Notes sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each tour does NOT cover, and roughly how much you'd spend on it yourself. Estimates use the yellow assumptions on the Notes sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Coverage check: who pays for what</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airport tax &amp; fuel surcharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 1.2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 2.3M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 1.15M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (group visa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 1.28M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 1.315M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipping (guide, driver, tour leader)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated · est. Rp 950k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 950k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · USD 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · USD 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 1.0M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 900k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPN / VAT 1.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra (rate not stated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (group, ≤69 y)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (up to USD 50k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra · Rp 600k (mandatory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (Zurich, ≤65 y)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included · 20 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (SQ fare; amount unreadable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included · 25 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (SQ fare; amount not stated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (SQ fare, per airline rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated · low-cost airline, check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meals on the plane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (Singapore Airlines)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · low-cost airline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meals in Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 6 meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 8 meals (no dinners)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 10 meals (no dinners)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 7 meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 9 meals (breakfast only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free day (no bus, no guide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included · every day guided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included · 1 day self-funded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile data / SIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (travel SIM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel &amp; airport porters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included (no porter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional tours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess baggage &amp; customs duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if solo · Rp 6.0M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if solo · Rp 7.0M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if solo · Rp 8.0M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if solo · Rp 7.5M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if solo · Rp 3.0M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine for skipping a compulsory shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if skipped · Rp 1M per shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated (visits compulsory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if skipped · Rp 3M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if skipped · Rp 4M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Already counted in the all-in price (Price sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airport tax &amp; fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPN / VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extras on top of the list price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Value NOT covered: estimated extra spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meals you buy in Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-day spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile data / eSIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel insurance (not stated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATED HIDDEN COSTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. True trip cost per adult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-in price (Price sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Estimated hidden costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE TRIP COST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True cost per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidden costs as % of all-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap to cheapest full-length tour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (5-day trip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. Risks: only if they happen (not added above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount sold out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked bag not in group fare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotte World entry not included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aviatour tipping higher than estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown: ask Aviatour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORST CASE (true cost + risks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not estimated because they depend on you: shopping, optional tours, excess baggage, single room, porter tips and drinks. Every operator excludes these, so they don't change the ranking. Change the yellow assumptions on the Notes sheet (meal cost, free-day spending, eSIM, insurance) to match your own habits.</t>
   </si>
   <si>
     <t xml:space="preserve">Days &amp; Flights</t>
@@ -831,9 +1262,6 @@
     <t xml:space="preserve">25 kg + 7 kg cabin</t>
   </si>
   <si>
-    <t xml:space="preserve">Not stated</t>
-  </si>
-  <si>
     <t xml:space="preserve">Per airline rules</t>
   </si>
   <si>
@@ -927,9 +1355,6 @@
     <t xml:space="preserve">2 nights · Layers Hotel Busan</t>
   </si>
   <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jeonju</t>
   </si>
   <si>
@@ -1546,6 +1971,48 @@
   </si>
   <si>
     <t xml:space="preserve">Obaja lists PPN as excluded without a rate. Assumed 1.1%, the rate every other operator uses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of a meal you buy yourself (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate for a casual restaurant meal in Korea (about KRW 12,000–15,000). Used on the Hidden Costs sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending per free day (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate for subway/taxi, one paid attraction and snacks on a no-bus, no-guide day (Obaja, Panorama).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korea eSIM / data for the trip (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate for a 5–8 day Korea data eSIM. Bayu Buana and Obaja include a travel SIM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel insurance if not included (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate for a 1-week Asia travel policy. Panorama's brochure does not say whether insurance is included: ask them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-cost airline meals, both flights (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotama flies Trinity Airways (ex-T'way), a low-cost carrier where meals are usually paid. Two ~7 h flights.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-cost airline checked bag, return (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if Rotama's group fare has no checked bag ("per airline rules"). Shown as a risk, not added to the estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotte World ticket if not included (IDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About KRW 62,000 for a 1-day adult pass. Wita implies entry is included; shown as a risk only.</t>
   </si>
   <si>
     <t xml:space="preserve">Legend</t>
@@ -1617,7 +2084,7 @@
     <numFmt numFmtId="174" formatCode="&quot;Rp &quot;#,##0"/>
     <numFmt numFmtId="175" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1781,6 +2248,46 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF8A6100"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB23B3B"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF3B5998"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF1F4E9A"/>
       <name val="Calibri"/>
@@ -1832,7 +2339,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1860,7 +2367,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFADADD"/>
-        <bgColor rgb="FFFCE4EC"/>
+        <bgColor rgb="FFFBE0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1872,7 +2379,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEFDF"/>
-        <bgColor rgb="FFE7E7E7"/>
+        <bgColor rgb="FFE3F4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -1884,13 +2391,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E7E7"/>
-        <bgColor rgb="FFE9E0F5"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
-        <bgColor rgb="FFFADADD"/>
+        <bgColor rgb="FFFBE0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1907,6 +2414,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3F4E4"/>
+        <bgColor rgb="FFEAF5EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFF1F1F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE0E0"/>
+        <bgColor rgb="FFFADADD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2FA"/>
+        <bgColor rgb="FFF1F1F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFBF7F9"/>
         <bgColor rgb="FFFFFBF7"/>
       </patternFill>
@@ -1914,13 +2445,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F1F1"/>
-        <bgColor rgb="FFEAF5EA"/>
+        <bgColor rgb="FFEEF2FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF5EA"/>
-        <bgColor rgb="FFF1F1F1"/>
+        <bgColor rgb="FFE3F4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -1979,7 +2510,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2100,6 +2631,30 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2108,15 +2663,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2132,23 +2687,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2156,7 +2711,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2164,7 +2719,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2172,19 +2727,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="27" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="27" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="27" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2192,7 +2747,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2212,55 +2767,55 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFF1F1F1"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF2E6B34"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF8A6100"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FFC2185B"/>
       <rgbColor rgb="FF1E4E8C"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF8E5BB5"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFE7E7E7"/>
       <rgbColor rgb="FFA3214F"/>
       <rgbColor rgb="FFFFF8D6"/>
-      <rgbColor rgb="FFEAF5EA"/>
+      <rgbColor rgb="FFE3F4E4"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFEEF2FA"/>
       <rgbColor rgb="FF1F4E9A"/>
       <rgbColor rgb="FFE8D9DE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFBF7"/>
+      <rgbColor rgb="FFF1F1F1"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFDCE8F5"/>
+      <rgbColor rgb="FFEAF5EA"/>
       <rgbColor rgb="FFDDEFDF"/>
       <rgbColor rgb="FFFFF1CC"/>
+      <rgbColor rgb="FFDCE8F5"/>
+      <rgbColor rgb="FFFBE0E0"/>
       <rgbColor rgb="FFE9E0F5"/>
+      <rgbColor rgb="FFFADADD"/>
+      <rgbColor rgb="FF3B5998"/>
+      <rgbColor rgb="FFFFFBF7"/>
+      <rgbColor rgb="FFFBF7F9"/>
       <rgbColor rgb="FFFCE4EC"/>
-      <rgbColor rgb="FFE7E7E7"/>
-      <rgbColor rgb="FFFADADD"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFBF7F9"/>
       <rgbColor rgb="FFD4A017"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFD9534F"/>
       <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF9CA3AF"/>
       <rgbColor rgb="FF1F3A5F"/>
       <rgbColor rgb="FF2E7D32"/>
       <rgbColor rgb="FF4B4B4B"/>
       <rgbColor rgb="FF222222"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FFC2185B"/>
+      <rgbColor rgb="FF555555"/>
+      <rgbColor rgb="FFB23B3B"/>
       <rgbColor rgb="FF5B3A8C"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
@@ -2449,7 +3004,7 @@
     <tabColor rgb="FFC2185B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2875,160 +3430,160 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!B36</f>
+        <v>1200000</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!C36</f>
+        <v>1400000</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!D36</f>
+        <v>2500000</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!E36</f>
+        <v>2575000</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!F36</f>
+        <v>1375000</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <f aca="false">'Hidden Costs'!G36</f>
+        <v>2025000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="13" t="str">
+      <c r="B21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!B40</f>
+        <v>28147290</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!C40</f>
+        <v>29983768</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!D40</f>
+        <v>22021900</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!E40</f>
+        <v>28225090</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!F40</f>
+        <v>30329850</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <f aca="false">'Hidden Costs'!G40</f>
+        <v>13328190</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!B41</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!C41</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!D41</f>
+        <v>2</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!E41</f>
+        <v>4</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!F41</f>
+        <v>6</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <f aca="false">'Hidden Costs'!G41</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="13" t="str">
         <f aca="false">Hotels!B7</f>
         <v>3★ or equivalent</v>
       </c>
-      <c r="C21" s="13" t="str">
+      <c r="C24" s="13" t="str">
         <f aca="false">Hotels!C7</f>
         <v>"Superior Class" (no stars stated)</v>
       </c>
-      <c r="D21" s="13" t="str">
+      <c r="D24" s="13" t="str">
         <f aca="false">Hotels!D7</f>
         <v>3★</v>
       </c>
-      <c r="E21" s="13" t="str">
+      <c r="E24" s="13" t="str">
         <f aca="false">Hotels!E7</f>
         <v>Not stated (named hotels)</v>
       </c>
-      <c r="F21" s="13" t="str">
+      <c r="F24" s="13" t="str">
         <f aca="false">Hotels!F7</f>
         <v>4★</v>
       </c>
-      <c r="G21" s="13" t="str">
+      <c r="G24" s="13" t="str">
         <f aca="false">Hotels!G7</f>
         <v>3★</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="13" t="str">
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="13" t="str">
         <f aca="false">Hotels!B10</f>
         <v>3 nights · 3★, "Seoul or nearby"</v>
       </c>
-      <c r="C22" s="13" t="str">
+      <c r="C25" s="13" t="str">
         <f aca="false">Hotels!C10</f>
         <v>3 nights · unnamed</v>
       </c>
-      <c r="D22" s="13" t="str">
+      <c r="D25" s="13" t="str">
         <f aca="false">Hotels!D10</f>
         <v>4 nights · Anyang Samwon Hotel</v>
       </c>
-      <c r="E22" s="13" t="str">
+      <c r="E25" s="13" t="str">
         <f aca="false">Hotels!E10</f>
         <v>4 nights · Baiton Dongdaemun Hotel</v>
       </c>
-      <c r="F22" s="13" t="str">
+      <c r="F25" s="13" t="str">
         <f aca="false">Hotels!F10</f>
         <v>3 nights · Migliore Hotel</v>
       </c>
-      <c r="G22" s="13" t="str">
+      <c r="G25" s="13" t="str">
         <f aca="false">Hotels!G10</f>
         <v>3 nights · Samwon Plaza Hotel</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <f aca="false">Hotels!B13</f>
-        <v>5</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <f aca="false">Hotels!C13</f>
-        <v>6</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <f aca="false">Hotels!D13</f>
-        <v>3</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <f aca="false">Hotels!E13</f>
-        <v>2</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <f aca="false">Hotels!F13</f>
-        <v>1</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <f aca="false">Hotels!G13</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="18" t="n">
-        <f aca="false">Meals!B19</f>
-        <v>12</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <f aca="false">Meals!C19</f>
-        <v>10</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <f aca="false">Meals!D19</f>
-        <v>8</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <f aca="false">Meals!E19</f>
-        <v>14</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <f aca="false">Meals!F19</f>
-        <v>11</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <f aca="false">Meals!G19</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!B20</f>
-        <v>20 kg + 7 kg cabin</v>
-      </c>
-      <c r="C25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!C20</f>
-        <v>Not legible (free cabin suitcase gift)</v>
-      </c>
-      <c r="D25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!D20</f>
-        <v>25 kg + 7 kg cabin</v>
-      </c>
-      <c r="E25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!E20</f>
-        <v>Not stated</v>
-      </c>
-      <c r="F25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!F20</f>
-        <v>Per airline rules</v>
-      </c>
-      <c r="G25" s="13" t="str">
-        <f aca="false">'Days &amp; Flights'!G20</f>
-        <v>Per airline rules (low-cost: check)</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3036,155 +3591,203 @@
         <v>35</v>
       </c>
       <c r="B26" s="14" t="n">
-        <f aca="false">Terms!B8</f>
+        <f aca="false">Hotels!B13</f>
         <v>5</v>
       </c>
       <c r="C26" s="14" t="n">
-        <f aca="false">Terms!C8</f>
+        <f aca="false">Hotels!C13</f>
         <v>6</v>
       </c>
       <c r="D26" s="14" t="n">
-        <f aca="false">Terms!D8</f>
-        <v>5</v>
+        <f aca="false">Hotels!D13</f>
+        <v>3</v>
       </c>
       <c r="E26" s="14" t="n">
-        <f aca="false">Terms!E8</f>
+        <f aca="false">Hotels!E13</f>
+        <v>2</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <f aca="false">Hotels!F13</f>
+        <v>1</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <f aca="false">Hotels!G13</f>
         <v>4</v>
       </c>
-      <c r="F26" s="14" t="n">
-        <f aca="false">Terms!F8</f>
-        <v>4</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <f aca="false">Terms!G8</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="18" t="n">
+        <f aca="false">Meals!B19</f>
+        <v>12</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <f aca="false">Meals!C19</f>
+        <v>10</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <f aca="false">Meals!D19</f>
+        <v>8</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <f aca="false">Meals!E19</f>
+        <v>14</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <f aca="false">Meals!F19</f>
+        <v>11</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <f aca="false">Meals!G19</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="18" t="n">
-        <f aca="false">Sightseeing!B56</f>
-        <v>18</v>
-      </c>
-      <c r="C28" s="18" t="n">
-        <f aca="false">Sightseeing!C56</f>
-        <v>15</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <f aca="false">Sightseeing!D56</f>
-        <v>9</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <f aca="false">Sightseeing!E56</f>
-        <v>19</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <f aca="false">Sightseeing!F56</f>
-        <v>18</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <f aca="false">Sightseeing!G56</f>
-        <v>13</v>
+      <c r="B28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!B20</f>
+        <v>20 kg + 7 kg cabin</v>
+      </c>
+      <c r="C28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!C20</f>
+        <v>Not legible (free cabin suitcase gift)</v>
+      </c>
+      <c r="D28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!D20</f>
+        <v>25 kg + 7 kg cabin</v>
+      </c>
+      <c r="E28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!E20</f>
+        <v>Not stated</v>
+      </c>
+      <c r="F28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!F20</f>
+        <v>Per airline rules</v>
+      </c>
+      <c r="G28" s="13" t="str">
+        <f aca="false">'Days &amp; Flights'!G20</f>
+        <v>Per airline rules (low-cost: check)</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="14" t="n">
+        <f aca="false">Terms!B8</f>
+        <v>5</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <f aca="false">Terms!C8</f>
+        <v>6</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <f aca="false">Terms!D8</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <f aca="false">Terms!E8</f>
+        <v>4</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <f aca="false">Terms!F8</f>
+        <v>4</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <f aca="false">Terms!G8</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="18" t="n">
+        <f aca="false">Sightseeing!B56</f>
+        <v>18</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <f aca="false">Sightseeing!C56</f>
+        <v>15</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <f aca="false">Sightseeing!D56</f>
+        <v>9</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <f aca="false">Sightseeing!E56</f>
+        <v>19</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <f aca="false">Sightseeing!F56</f>
+        <v>18</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <f aca="false">Sightseeing!G56</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!B14</f>
         <v>3.85714285714286</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!C14</f>
         <v>3.57142857142857</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!D14</f>
         <v>2.14285714285714</v>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!E14</f>
         <v>4.14285714285714</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!F14</f>
         <v>4</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G32" s="19" t="n">
         <f aca="false">'Sightseeing Opinion'!G14</f>
         <v>2.42857142857143</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
+    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
@@ -3194,10 +3797,10 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
@@ -3207,10 +3810,10 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="20"/>
@@ -3220,10 +3823,10 @@
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
@@ -3231,16 +3834,55 @@
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
     </row>
-    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+    <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+    </row>
+    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
+      <c r="B40" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+    </row>
+    <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3248,17 +3890,17 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G38"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <conditionalFormatting sqref="B16:G16">
     <cfRule type="colorScale" priority="2">
@@ -3296,7 +3938,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:G23">
+  <conditionalFormatting sqref="B20:G20">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -3308,15 +3950,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24:G24">
+  <conditionalFormatting sqref="B21:G21">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
         <color rgb="FFF8C8C8"/>
-        <color rgb="FFFFF4CC"/>
-        <color rgb="FFC8E6C9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -3332,7 +3974,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:G28">
+  <conditionalFormatting sqref="B27:G27">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -3350,12 +3992,333 @@
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:G31">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFF8C8C8"/>
         <color rgb="FFFFF4CC"/>
         <color rgb="FFC8E6C9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B32:G32">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8C8C8"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFC8E6C9"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF9CA3AF"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="B7" s="56" t="n">
+        <v>950000</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="53" t="s">
+        <v>462</v>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="53" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" s="56" t="n">
+        <v>175000</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="53" t="s">
+        <v>466</v>
+      </c>
+      <c r="B10" s="56" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="53" t="s">
+        <v>468</v>
+      </c>
+      <c r="B11" s="56" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="53" t="s">
+        <v>470</v>
+      </c>
+      <c r="B12" s="56" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="53" t="s">
+        <v>472</v>
+      </c>
+      <c r="B13" s="56" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="53" t="s">
+        <v>474</v>
+      </c>
+      <c r="B14" s="56" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="53" t="s">
+        <v>476</v>
+      </c>
+      <c r="B15" s="56" t="n">
+        <v>730000</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="58" t="s">
+        <v>479</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>480</v>
+      </c>
+      <c r="C18" s="59"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="s">
+        <v>481</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="C19" s="59"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="58" t="s">
+        <v>483</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>484</v>
+      </c>
+      <c r="C20" s="59"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
+        <v>485</v>
+      </c>
+      <c r="B21" s="59" t="s">
+        <v>486</v>
+      </c>
+      <c r="C21" s="59"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="58" t="s">
+        <v>487</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>488</v>
+      </c>
+      <c r="C22" s="59"/>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="59" t="s">
+        <v>490</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="59" t="s">
+        <v>491</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="59" t="s">
+        <v>492</v>
+      </c>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="59" t="s">
+        <v>493</v>
+      </c>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="59" t="s">
+        <v>494</v>
+      </c>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3382,7 +4345,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3393,7 +4356,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3436,7 +4399,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -3447,7 +4410,7 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>23390000</v>
@@ -3470,7 +4433,7 @@
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>23390000</v>
@@ -3493,7 +4456,7 @@
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B9" s="22" t="n">
         <v>23390000</v>
@@ -3516,7 +4479,7 @@
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>22890000</v>
@@ -3539,7 +4502,7 @@
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -3575,7 +4538,7 @@
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3586,7 +4549,7 @@
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="23" t="n">
         <v>1200000</v>
@@ -3609,7 +4572,7 @@
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>1150000</v>
@@ -3632,7 +4595,7 @@
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -3647,7 +4610,7 @@
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" s="15" t="n">
         <f aca="false">Notes!$B$7</f>
@@ -3673,7 +4636,7 @@
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>0</v>
@@ -3696,7 +4659,7 @@
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>0.011</v>
@@ -3720,7 +4683,7 @@
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B20" s="15" t="n">
         <f aca="false">B7*B19</f>
@@ -3749,7 +4712,7 @@
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B21" s="22" t="n">
         <v>0</v>
@@ -3772,7 +4735,7 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3783,7 +4746,7 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">B7+B14+B15+B17+B18+B20+B21</f>
@@ -3812,7 +4775,7 @@
     </row>
     <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="22" t="n">
@@ -3831,7 +4794,7 @@
     </row>
     <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" s="29" t="str">
         <f aca="false">IF(B24="","",B23-B24)</f>
@@ -3889,7 +4852,7 @@
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3900,7 +4863,7 @@
     </row>
     <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B28" s="17" t="n">
         <f aca="false">B23/'Days &amp; Flights'!B9</f>
@@ -3929,7 +4892,7 @@
     </row>
     <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B29" s="17" t="n">
         <f aca="false">B23/'Days &amp; Flights'!B10</f>
@@ -3958,7 +4921,7 @@
     </row>
     <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B30" s="17" t="n">
         <f aca="false">B23/'Days &amp; Flights'!B11</f>
@@ -3987,7 +4950,7 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -4080,6 +5043,1269 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFD9534F"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="15" t="n">
+        <f aca="false">Price!B14</f>
+        <v>1200000</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">Price!C14</f>
+        <v>2300000</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <f aca="false">Price!D14</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <f aca="false">Price!E14</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <f aca="false">Price!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <f aca="false">Price!G14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="15" t="n">
+        <f aca="false">Price!B15</f>
+        <v>1150000</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">Price!C15</f>
+        <v>1150000</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <f aca="false">Price!D15</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <f aca="false">Price!E15</f>
+        <v>1281000</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <f aca="false">Price!F15</f>
+        <v>1315000</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <f aca="false">Price!G15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <f aca="false">Price!B17</f>
+        <v>950000</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <f aca="false">Price!C17</f>
+        <v>950000</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <f aca="false">Price!D17</f>
+        <v>825000</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <f aca="false">Price!E17</f>
+        <v>924000</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <f aca="false">Price!F17</f>
+        <v>1000000</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <f aca="false">Price!G17</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="15" t="n">
+        <f aca="false">Price!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">Price!C18</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <f aca="false">Price!D18</f>
+        <v>600000</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <f aca="false">Price!E18</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <f aca="false">Price!F18</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <f aca="false">Price!G18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <f aca="false">Price!B20</f>
+        <v>257290</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <f aca="false">Price!C20</f>
+        <v>295768</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <f aca="false">Price!D20</f>
+        <v>196900</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <f aca="false">Price!E20</f>
+        <v>255090</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <f aca="false">Price!F20</f>
+        <v>289850</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <f aca="false">Price!G20</f>
+        <v>113190</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="15" t="n">
+        <f aca="false">Price!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <f aca="false">Price!C21</f>
+        <v>-3000000</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <f aca="false">Price!D21</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <f aca="false">Price!E21</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <f aca="false">Price!F21</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <f aca="false">Price!G21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" s="35" t="n">
+        <f aca="false">SUM(B23:B28)</f>
+        <v>3557290</v>
+      </c>
+      <c r="C29" s="35" t="n">
+        <f aca="false">SUM(C23:C28)</f>
+        <v>1695768</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <f aca="false">SUM(D23:D28)</f>
+        <v>1621900</v>
+      </c>
+      <c r="E29" s="35" t="n">
+        <f aca="false">SUM(E23:E28)</f>
+        <v>2460090</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <f aca="false">SUM(F23:F28)</f>
+        <v>2604850</v>
+      </c>
+      <c r="G29" s="35" t="n">
+        <f aca="false">SUM(G23:G28)</f>
+        <v>1013190</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="15" t="n">
+        <f aca="false">Meals!B20*Notes!$B$9</f>
+        <v>1050000</v>
+      </c>
+      <c r="C31" s="15" t="n">
+        <f aca="false">Meals!C20*Notes!$B$9</f>
+        <v>1400000</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <f aca="false">Meals!D20*Notes!$B$9</f>
+        <v>1750000</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <f aca="false">Meals!E20*Notes!$B$9</f>
+        <v>1225000</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <f aca="false">Meals!F20*Notes!$B$9</f>
+        <v>1225000</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <f aca="false">Meals!G20*Notes!$B$9</f>
+        <v>1575000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!B12*Notes!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!C12*Notes!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!D12*Notes!$B$10</f>
+        <v>750000</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!E12*Notes!$B$10</f>
+        <v>750000</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!F12*Notes!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <f aca="false">'Days &amp; Flights'!G12*Notes!$B$10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B33" s="15" t="n">
+        <f aca="false">Notes!$B$11</f>
+        <v>150000</v>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <f aca="false">Notes!$B$11</f>
+        <v>150000</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <f aca="false">Notes!$B$11</f>
+        <v>150000</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <f aca="false">Notes!$B$11</f>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <f aca="false">Notes!$B$12</f>
+        <v>450000</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <f aca="false">Notes!$B$13</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="28" t="n">
+        <f aca="false">SUM(B31:B35)</f>
+        <v>1200000</v>
+      </c>
+      <c r="C36" s="28" t="n">
+        <f aca="false">SUM(C31:C35)</f>
+        <v>1400000</v>
+      </c>
+      <c r="D36" s="28" t="n">
+        <f aca="false">SUM(D31:D35)</f>
+        <v>2500000</v>
+      </c>
+      <c r="E36" s="28" t="n">
+        <f aca="false">SUM(E31:E35)</f>
+        <v>2575000</v>
+      </c>
+      <c r="F36" s="28" t="n">
+        <f aca="false">SUM(F31:F35)</f>
+        <v>1375000</v>
+      </c>
+      <c r="G36" s="28" t="n">
+        <f aca="false">SUM(G31:G35)</f>
+        <v>2025000</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="15" t="n">
+        <f aca="false">Price!B23</f>
+        <v>26947290</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <f aca="false">Price!C23</f>
+        <v>28583768</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <f aca="false">Price!D23</f>
+        <v>19521900</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <f aca="false">Price!E23</f>
+        <v>25650090</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <f aca="false">Price!F23</f>
+        <v>28954850</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <f aca="false">Price!G23</f>
+        <v>11303190</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="15" t="n">
+        <f aca="false">B36</f>
+        <v>1200000</v>
+      </c>
+      <c r="C39" s="15" t="n">
+        <f aca="false">C36</f>
+        <v>1400000</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <f aca="false">D36</f>
+        <v>2500000</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <f aca="false">E36</f>
+        <v>2575000</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <f aca="false">F36</f>
+        <v>1375000</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <f aca="false">G36</f>
+        <v>2025000</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="16" t="n">
+        <f aca="false">B38+B36</f>
+        <v>28147290</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <f aca="false">C38+C36</f>
+        <v>29983768</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <f aca="false">D38+D36</f>
+        <v>22021900</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <f aca="false">E38+E36</f>
+        <v>28225090</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <f aca="false">F38+F36</f>
+        <v>30329850</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <f aca="false">G38+G36</f>
+        <v>13328190</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="18" t="n">
+        <f aca="false">RANK(B40,$B$40:$G$40,1)</f>
+        <v>3</v>
+      </c>
+      <c r="C41" s="18" t="n">
+        <f aca="false">RANK(C40,$B$40:$G$40,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <f aca="false">RANK(D40,$B$40:$G$40,1)</f>
+        <v>2</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <f aca="false">RANK(E40,$B$40:$G$40,1)</f>
+        <v>4</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <f aca="false">RANK(F40,$B$40:$G$40,1)</f>
+        <v>6</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <f aca="false">RANK(G40,$B$40:$G$40,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="17" t="n">
+        <f aca="false">B40/'Days &amp; Flights'!B9</f>
+        <v>4021041.42857143</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <f aca="false">C40/'Days &amp; Flights'!C9</f>
+        <v>4283395.42857143</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <f aca="false">D40/'Days &amp; Flights'!D9</f>
+        <v>3145985.71428571</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <f aca="false">E40/'Days &amp; Flights'!E9</f>
+        <v>3528136.25</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <f aca="false">F40/'Days &amp; Flights'!F9</f>
+        <v>4332835.71428572</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <f aca="false">G40/'Days &amp; Flights'!G9</f>
+        <v>2665638</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="27" t="n">
+        <f aca="false">B36/B38</f>
+        <v>0.0445313795932726</v>
+      </c>
+      <c r="C43" s="27" t="n">
+        <f aca="false">C36/C38</f>
+        <v>0.0489788470155509</v>
+      </c>
+      <c r="D43" s="27" t="n">
+        <f aca="false">D36/D38</f>
+        <v>0.128061305508173</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <f aca="false">E36/E38</f>
+        <v>0.100389511303859</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <f aca="false">F36/F38</f>
+        <v>0.0474877265812118</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <f aca="false">G36/G38</f>
+        <v>0.179152964782508</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="15" t="n">
+        <f aca="false">B40-MIN($B$40:$F$40)</f>
+        <v>6125390</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <f aca="false">C40-MIN($B$40:$F$40)</f>
+        <v>7961868</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <f aca="false">D40-MIN($B$40:$F$40)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <f aca="false">E40-MIN($B$40:$F$40)</f>
+        <v>6203190</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <f aca="false">F40-MIN($B$40:$F$40)</f>
+        <v>8307950</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <f aca="false">Notes!$B$14</f>
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <f aca="false">Notes!$B$15</f>
+        <v>730000</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="35" t="n">
+        <f aca="false">B40+SUM(B46:B48)</f>
+        <v>28147290</v>
+      </c>
+      <c r="C50" s="35" t="n">
+        <f aca="false">C40+SUM(C46:C48)</f>
+        <v>32983768</v>
+      </c>
+      <c r="D50" s="35" t="n">
+        <f aca="false">D40+SUM(D46:D48)</f>
+        <v>22021900</v>
+      </c>
+      <c r="E50" s="35" t="n">
+        <f aca="false">E40+SUM(E46:E48)</f>
+        <v>28225090</v>
+      </c>
+      <c r="F50" s="35" t="n">
+        <f aca="false">F40+SUM(F46:F48)</f>
+        <v>31059850</v>
+      </c>
+      <c r="G50" s="35" t="n">
+        <f aca="false">G40+SUM(G46:G48)</f>
+        <v>14078190</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A52:G52"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B29:G29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36:G36">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:G40">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:G42">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:G43">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:G50">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC8E6C9"/>
+        <color rgb="FFFFF4CC"/>
+        <color rgb="FFF8C8C8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -4093,7 +6319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4104,7 +6330,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4147,7 +6373,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4161,90 +6387,90 @@
         <v>10</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="30" t="n">
+        <v>191</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="36" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="30" t="n">
+        <v>192</v>
+      </c>
+      <c r="B10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="36" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4252,51 +6478,51 @@
       <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="31" t="n">
+        <v>193</v>
+      </c>
+      <c r="B12" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="31" t="n">
+      <c r="C12" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4310,114 +6536,114 @@
         <v>20</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>100</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>111</v>
+        <v>207</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>118</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>122</v>
+        <v>218</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>123</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4425,68 +6651,68 @@
         <v>21</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4502,30 +6728,30 @@
     </row>
     <row r="23" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>141</v>
+        <v>236</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>142</v>
+        <v>237</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>147</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -4565,7 +6791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
@@ -4581,7 +6807,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4592,7 +6818,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4635,7 +6861,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>151</v>
+        <v>246</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4646,168 +6872,168 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>157</v>
+        <v>252</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>160</v>
+        <v>255</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>168</v>
+        <v>262</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>169</v>
+        <v>263</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>179</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>182</v>
+        <v>276</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>183</v>
+        <v>277</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>185</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="B13" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="38" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -4846,7 +7072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
@@ -4862,7 +7088,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>281</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4873,7 +7099,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>282</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4916,7 +7142,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>189</v>
+        <v>283</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4927,177 +7153,177 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>190</v>
+        <v>284</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>163</v>
+        <v>285</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>197</v>
+        <v>292</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="G12" s="34"/>
+        <v>294</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>201</v>
+        <v>295</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="34"/>
+        <v>291</v>
+      </c>
+      <c r="G13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
+        <v>296</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5108,7 +7334,7 @@
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="B16" s="14" t="n">
         <f aca="false">COUNTIF(B7:B14,"*B*")</f>
@@ -5137,7 +7363,7 @@
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>205</v>
+        <v>299</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">COUNTIF(B7:B14,"*L*")</f>
@@ -5166,7 +7392,7 @@
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">COUNTIF(B7:B14,"*D*")</f>
@@ -5195,36 +7421,36 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="35" t="n">
+        <v>301</v>
+      </c>
+      <c r="B19" s="41" t="n">
         <f aca="false">SUM(B16:B18)</f>
         <v>12</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="41" t="n">
         <f aca="false">SUM(C16:C18)</f>
         <v>10</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="41" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>8</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="41" t="n">
         <f aca="false">SUM(E16:E18)</f>
         <v>14</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="41" t="n">
         <f aca="false">SUM(F16:F18)</f>
         <v>11</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="41" t="n">
         <f aca="false">SUM(G16:G18)</f>
         <v>3</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>208</v>
+        <v>302</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">'Days &amp; Flights'!B10*3-B19+3</f>
@@ -5253,25 +7479,25 @@
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>209</v>
+        <v>303</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>210</v>
+        <v>304</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>212</v>
+        <v>306</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>213</v>
+        <v>307</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>215</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5316,7 +7542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1F3A5F"/>
@@ -5332,7 +7558,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5343,7 +7569,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5386,7 +7612,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>218</v>
+        <v>312</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5397,70 +7623,70 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>219</v>
+        <v>313</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>223</v>
+        <v>317</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>223</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="B8" s="30" t="n">
+        <v>318</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="36" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37" t="n">
+        <v>319</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43" t="n">
         <v>1000000</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37" t="n">
+      <c r="E9" s="42"/>
+      <c r="F9" s="43" t="n">
         <v>3000000</v>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G9" s="43" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>226</v>
+        <v>320</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5471,99 +7697,99 @@
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>227</v>
+        <v>321</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>228</v>
+        <v>322</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>228</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>230</v>
+        <v>324</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>231</v>
+        <v>325</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>233</v>
+        <v>327</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>235</v>
+        <v>329</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>236</v>
+        <v>330</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>238</v>
+        <v>332</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>238</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>239</v>
+        <v>333</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>240</v>
+        <v>334</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>241</v>
+        <v>335</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>242</v>
+        <v>336</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>242</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5574,53 +7800,53 @@
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>245</v>
+        <v>339</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>246</v>
+        <v>340</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>248</v>
+        <v>342</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>249</v>
+        <v>343</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>250</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>251</v>
+        <v>345</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>253</v>
+        <v>347</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -5661,7 +7887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8E5BB5"/>
@@ -5677,7 +7903,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5688,7 +7914,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5708,7 +7934,7 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>256</v>
+        <v>350</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -5731,7 +7957,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>157</v>
+        <v>252</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5742,214 +7968,214 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>163</v>
+        <v>351</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>163</v>
+        <v>353</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>163</v>
+        <v>354</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" s="40" t="s">
-        <v>163</v>
+        <v>355</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>163</v>
+        <v>357</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G12" s="40" t="s">
-        <v>163</v>
+        <v>358</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>163</v>
+        <v>359</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G14" s="40" t="s">
-        <v>163</v>
+        <v>360</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>163</v>
+        <v>361</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5960,99 +8186,99 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>163</v>
+        <v>364</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>163</v>
+        <v>367</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>163</v>
+        <v>368</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>163</v>
+        <v>369</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6063,145 +8289,145 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>163</v>
+        <v>371</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>163</v>
+        <v>373</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>163</v>
+        <v>374</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="40" t="s">
-        <v>163</v>
+        <v>375</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>163</v>
+        <v>376</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G27" s="40" t="s">
-        <v>163</v>
+        <v>377</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>284</v>
+        <v>378</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6212,444 +8438,444 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>258</v>
+        <v>379</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="G30" s="40" t="s">
-        <v>163</v>
+        <v>381</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>163</v>
+        <v>382</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G32" s="40" t="s">
-        <v>163</v>
+        <v>383</v>
+      </c>
+      <c r="B32" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>163</v>
+        <v>384</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="B34" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>258</v>
+        <v>385</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F35" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>258</v>
+        <v>386</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="B36" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F36" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G36" s="40" t="s">
-        <v>163</v>
+        <v>387</v>
+      </c>
+      <c r="B36" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>295</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>258</v>
+        <v>388</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>389</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D38" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F38" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>258</v>
+        <v>391</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C38" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B39" s="43" t="s">
-        <v>299</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G39" s="38" t="s">
-        <v>258</v>
+        <v>392</v>
+      </c>
+      <c r="B39" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D40" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>258</v>
+        <v>394</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F40" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="B41" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>163</v>
+        <v>395</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" s="44" t="s">
+        <v>396</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="B42" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>258</v>
+        <v>397</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D42" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G43" s="38" t="s">
-        <v>258</v>
+        <v>398</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E43" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B44" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C44" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D44" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F44" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G44" s="40" t="s">
-        <v>163</v>
+        <v>399</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F44" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G44" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>163</v>
+        <v>400</v>
+      </c>
+      <c r="B45" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="B46" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D46" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>258</v>
+        <v>401</v>
+      </c>
+      <c r="B46" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F46" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G47" s="38" t="s">
-        <v>258</v>
+        <v>402</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -6660,145 +8886,145 @@
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="G49" s="38" t="s">
-        <v>258</v>
+        <v>404</v>
+      </c>
+      <c r="B49" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="E49" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="F49" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G50" s="40" t="s">
-        <v>163</v>
+        <v>407</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E50" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F50" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G50" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D51" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E51" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F51" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>258</v>
+        <v>309</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B52" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D52" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E52" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G52" s="40" t="s">
-        <v>163</v>
+        <v>408</v>
+      </c>
+      <c r="B52" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D52" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G52" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="B53" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C53" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D53" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E53" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F53" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="G53" s="39" t="s">
-        <v>163</v>
+        <v>409</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F53" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="B54" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C54" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="E54" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="F54" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G54" s="40" t="s">
-        <v>163</v>
+        <v>410</v>
+      </c>
+      <c r="B54" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="E54" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="F54" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G54" s="46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>318</v>
+        <v>412</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -6809,36 +9035,36 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="B56" s="35" t="n">
+        <v>413</v>
+      </c>
+      <c r="B56" s="41" t="n">
         <f aca="false">COUNTIF(B6:B54,"✓*")</f>
         <v>18</v>
       </c>
-      <c r="C56" s="35" t="n">
+      <c r="C56" s="41" t="n">
         <f aca="false">COUNTIF(C6:C54,"✓*")</f>
         <v>15</v>
       </c>
-      <c r="D56" s="35" t="n">
+      <c r="D56" s="41" t="n">
         <f aca="false">COUNTIF(D6:D54,"✓*")</f>
         <v>9</v>
       </c>
-      <c r="E56" s="35" t="n">
+      <c r="E56" s="41" t="n">
         <f aca="false">COUNTIF(E6:E54,"✓*")</f>
         <v>19</v>
       </c>
-      <c r="F56" s="35" t="n">
+      <c r="F56" s="41" t="n">
         <f aca="false">COUNTIF(F6:F54,"✓*")</f>
         <v>18</v>
       </c>
-      <c r="G56" s="35" t="n">
+      <c r="G56" s="41" t="n">
         <f aca="false">COUNTIF(G6:G54,"✓*")</f>
         <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>320</v>
+        <v>414</v>
       </c>
       <c r="B57" s="14" t="n">
         <f aca="false">COUNTIF(B6:B54,"Photo stop")</f>
@@ -6867,7 +9093,7 @@
     </row>
     <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>321</v>
+        <v>415</v>
       </c>
       <c r="B58" s="19" t="n">
         <f aca="false">B56/'Days &amp; Flights'!B11</f>
@@ -6896,7 +9122,7 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>322</v>
+        <v>416</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -6951,7 +9177,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8E5BB5"/>
@@ -6967,7 +9193,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6978,7 +9204,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>418</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6998,7 +9224,7 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>325</v>
+        <v>419</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -7021,7 +9247,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>326</v>
+        <v>420</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -7032,197 +9258,197 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="30" t="n">
+        <v>421</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B8" s="30" t="n">
+        <v>422</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="B9" s="30" t="n">
+        <v>423</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="30" t="n">
+        <v>424</v>
+      </c>
+      <c r="B10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="36" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B11" s="30" t="n">
+        <v>425</v>
+      </c>
+      <c r="B11" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="B12" s="30" t="n">
+        <v>426</v>
+      </c>
+      <c r="B12" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B13" s="30" t="n">
+        <v>427</v>
+      </c>
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="B14" s="45" t="n">
+        <v>428</v>
+      </c>
+      <c r="B14" s="51" t="n">
         <f aca="false">AVERAGE(B7:B13)</f>
         <v>3.85714285714286</v>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C14" s="51" t="n">
         <f aca="false">AVERAGE(C7:C13)</f>
         <v>3.57142857142857</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="51" t="n">
         <f aca="false">AVERAGE(D7:D13)</f>
         <v>2.14285714285714</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="51" t="n">
         <f aca="false">AVERAGE(E7:E13)</f>
         <v>4.14285714285714</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="51" t="n">
         <f aca="false">AVERAGE(F7:F13)</f>
         <v>4</v>
       </c>
-      <c r="G14" s="45" t="n">
+      <c r="G14" s="51" t="n">
         <f aca="false">AVERAGE(G7:G13)</f>
         <v>2.42857142857143</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>335</v>
+        <v>429</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">RANK(B14,$B$14:$G$14,0)</f>
@@ -7251,7 +9477,7 @@
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7262,210 +9488,210 @@
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="B17" s="46" t="str">
+        <v>421</v>
+      </c>
+      <c r="B17" s="52" t="str">
         <f aca="false">REPT("★",B7)&amp;REPT("☆",5-B7)</f>
         <v>★★★★★</v>
       </c>
-      <c r="C17" s="46" t="str">
+      <c r="C17" s="52" t="str">
         <f aca="false">REPT("★",C7)&amp;REPT("☆",5-C7)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="D17" s="46" t="str">
+      <c r="D17" s="52" t="str">
         <f aca="false">REPT("★",D7)&amp;REPT("☆",5-D7)</f>
         <v>★★☆☆☆</v>
       </c>
-      <c r="E17" s="46" t="str">
+      <c r="E17" s="52" t="str">
         <f aca="false">REPT("★",E7)&amp;REPT("☆",5-E7)</f>
         <v>★★★★★</v>
       </c>
-      <c r="F17" s="46" t="str">
+      <c r="F17" s="52" t="str">
         <f aca="false">REPT("★",F7)&amp;REPT("☆",5-F7)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="G17" s="46" t="str">
+      <c r="G17" s="52" t="str">
         <f aca="false">REPT("★",G7)&amp;REPT("☆",5-G7)</f>
         <v>★★★☆☆</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B18" s="46" t="str">
+        <v>422</v>
+      </c>
+      <c r="B18" s="52" t="str">
         <f aca="false">REPT("★",B8)&amp;REPT("☆",5-B8)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="C18" s="46" t="str">
+      <c r="C18" s="52" t="str">
         <f aca="false">REPT("★",C8)&amp;REPT("☆",5-C8)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="D18" s="46" t="str">
+      <c r="D18" s="52" t="str">
         <f aca="false">REPT("★",D8)&amp;REPT("☆",5-D8)</f>
         <v>★☆☆☆☆</v>
       </c>
-      <c r="E18" s="46" t="str">
+      <c r="E18" s="52" t="str">
         <f aca="false">REPT("★",E8)&amp;REPT("☆",5-E8)</f>
         <v>★☆☆☆☆</v>
       </c>
-      <c r="F18" s="46" t="str">
+      <c r="F18" s="52" t="str">
         <f aca="false">REPT("★",F8)&amp;REPT("☆",5-F8)</f>
         <v>★★★★★</v>
       </c>
-      <c r="G18" s="46" t="str">
+      <c r="G18" s="52" t="str">
         <f aca="false">REPT("★",G8)&amp;REPT("☆",5-G8)</f>
         <v>☆☆☆☆☆</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="B19" s="46" t="str">
+        <v>423</v>
+      </c>
+      <c r="B19" s="52" t="str">
         <f aca="false">REPT("★",B9)&amp;REPT("☆",5-B9)</f>
         <v>★★★★★</v>
       </c>
-      <c r="C19" s="46" t="str">
+      <c r="C19" s="52" t="str">
         <f aca="false">REPT("★",C9)&amp;REPT("☆",5-C9)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="D19" s="46" t="str">
+      <c r="D19" s="52" t="str">
         <f aca="false">REPT("★",D9)&amp;REPT("☆",5-D9)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="E19" s="46" t="str">
+      <c r="E19" s="52" t="str">
         <f aca="false">REPT("★",E9)&amp;REPT("☆",5-E9)</f>
         <v>★★★★★</v>
       </c>
-      <c r="F19" s="46" t="str">
+      <c r="F19" s="52" t="str">
         <f aca="false">REPT("★",F9)&amp;REPT("☆",5-F9)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="G19" s="46" t="str">
+      <c r="G19" s="52" t="str">
         <f aca="false">REPT("★",G9)&amp;REPT("☆",5-G9)</f>
         <v>★★★☆☆</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="46" t="str">
+        <v>424</v>
+      </c>
+      <c r="B20" s="52" t="str">
         <f aca="false">REPT("★",B10)&amp;REPT("☆",5-B10)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="C20" s="46" t="str">
+      <c r="C20" s="52" t="str">
         <f aca="false">REPT("★",C10)&amp;REPT("☆",5-C10)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="D20" s="46" t="str">
+      <c r="D20" s="52" t="str">
         <f aca="false">REPT("★",D10)&amp;REPT("☆",5-D10)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="E20" s="46" t="str">
+      <c r="E20" s="52" t="str">
         <f aca="false">REPT("★",E10)&amp;REPT("☆",5-E10)</f>
         <v>★★★★★</v>
       </c>
-      <c r="F20" s="46" t="str">
+      <c r="F20" s="52" t="str">
         <f aca="false">REPT("★",F10)&amp;REPT("☆",5-F10)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="G20" s="46" t="str">
+      <c r="G20" s="52" t="str">
         <f aca="false">REPT("★",G10)&amp;REPT("☆",5-G10)</f>
         <v>★★☆☆☆</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B21" s="46" t="str">
+        <v>425</v>
+      </c>
+      <c r="B21" s="52" t="str">
         <f aca="false">REPT("★",B11)&amp;REPT("☆",5-B11)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="C21" s="46" t="str">
+      <c r="C21" s="52" t="str">
         <f aca="false">REPT("★",C11)&amp;REPT("☆",5-C11)</f>
         <v>★★★★★</v>
       </c>
-      <c r="D21" s="46" t="str">
+      <c r="D21" s="52" t="str">
         <f aca="false">REPT("★",D11)&amp;REPT("☆",5-D11)</f>
         <v>★★☆☆☆</v>
       </c>
-      <c r="E21" s="46" t="str">
+      <c r="E21" s="52" t="str">
         <f aca="false">REPT("★",E11)&amp;REPT("☆",5-E11)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="F21" s="46" t="str">
+      <c r="F21" s="52" t="str">
         <f aca="false">REPT("★",F11)&amp;REPT("☆",5-F11)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="G21" s="46" t="str">
+      <c r="G21" s="52" t="str">
         <f aca="false">REPT("★",G11)&amp;REPT("☆",5-G11)</f>
         <v>★★★☆☆</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="B22" s="46" t="str">
+        <v>426</v>
+      </c>
+      <c r="B22" s="52" t="str">
         <f aca="false">REPT("★",B12)&amp;REPT("☆",5-B12)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="C22" s="46" t="str">
+      <c r="C22" s="52" t="str">
         <f aca="false">REPT("★",C12)&amp;REPT("☆",5-C12)</f>
         <v>★★☆☆☆</v>
       </c>
-      <c r="D22" s="46" t="str">
+      <c r="D22" s="52" t="str">
         <f aca="false">REPT("★",D12)&amp;REPT("☆",5-D12)</f>
         <v>★★☆☆☆</v>
       </c>
-      <c r="E22" s="46" t="str">
+      <c r="E22" s="52" t="str">
         <f aca="false">REPT("★",E12)&amp;REPT("☆",5-E12)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="F22" s="46" t="str">
+      <c r="F22" s="52" t="str">
         <f aca="false">REPT("★",F12)&amp;REPT("☆",5-F12)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="G22" s="46" t="str">
+      <c r="G22" s="52" t="str">
         <f aca="false">REPT("★",G12)&amp;REPT("☆",5-G12)</f>
         <v>★★★☆☆</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B23" s="46" t="str">
+        <v>427</v>
+      </c>
+      <c r="B23" s="52" t="str">
         <f aca="false">REPT("★",B13)&amp;REPT("☆",5-B13)</f>
         <v>★★★☆☆</v>
       </c>
-      <c r="C23" s="46" t="str">
+      <c r="C23" s="52" t="str">
         <f aca="false">REPT("★",C13)&amp;REPT("☆",5-C13)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="D23" s="46" t="str">
+      <c r="D23" s="52" t="str">
         <f aca="false">REPT("★",D13)&amp;REPT("☆",5-D13)</f>
         <v>★★☆☆☆</v>
       </c>
-      <c r="E23" s="46" t="str">
+      <c r="E23" s="52" t="str">
         <f aca="false">REPT("★",E13)&amp;REPT("☆",5-E13)</f>
         <v>★★★★★</v>
       </c>
-      <c r="F23" s="46" t="str">
+      <c r="F23" s="52" t="str">
         <f aca="false">REPT("★",F13)&amp;REPT("☆",5-F13)</f>
         <v>★★★★☆</v>
       </c>
-      <c r="G23" s="46" t="str">
+      <c r="G23" s="52" t="str">
         <f aca="false">REPT("★",G13)&amp;REPT("☆",5-G13)</f>
         <v>★★★☆☆</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>337</v>
+        <v>431</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7476,71 +9702,71 @@
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>338</v>
+        <v>432</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>339</v>
+        <v>433</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>340</v>
+        <v>434</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>341</v>
+        <v>435</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>342</v>
+        <v>436</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>343</v>
+        <v>437</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>344</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>345</v>
+        <v>439</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>346</v>
+        <v>440</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>347</v>
+        <v>441</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>348</v>
+        <v>442</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>351</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>353</v>
+        <v>447</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>355</v>
+        <v>449</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>356</v>
+        <v>450</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>357</v>
+        <v>451</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>358</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -7572,224 +9798,4 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF9CA3AF"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>364</v>
-      </c>
-      <c r="B6" s="48" t="n">
-        <v>16500</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>366</v>
-      </c>
-      <c r="B7" s="50" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>368</v>
-      </c>
-      <c r="B8" s="51" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="53" t="s">
-        <v>372</v>
-      </c>
-      <c r="C11" s="53"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
-        <v>373</v>
-      </c>
-      <c r="B12" s="53" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="53"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="B13" s="53" t="s">
-        <v>376</v>
-      </c>
-      <c r="C13" s="53"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
-        <v>377</v>
-      </c>
-      <c r="B14" s="53" t="s">
-        <v>378</v>
-      </c>
-      <c r="C14" s="53"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="52" t="s">
-        <v>379</v>
-      </c>
-      <c r="B15" s="53" t="s">
-        <v>380</v>
-      </c>
-      <c r="C15" s="53"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="s">
-        <v>382</v>
-      </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="53" t="s">
-        <v>383</v>
-      </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="53" t="s">
-        <v>384</v>
-      </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="53" t="s">
-        <v>385</v>
-      </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="53" t="s">
-        <v>386</v>
-      </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>